--- a/data/2026-04-27/SCW Weekly Comp 2026-04-27 (Responses).xlsx
+++ b/data/2026-04-27/SCW Weekly Comp 2026-04-27 (Responses).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="318">
   <si>
     <t>Timestamp</t>
   </si>
@@ -898,7 +898,61 @@
     <t>3:16.44</t>
   </si>
   <si>
-    <t>https://www.facebook.com/events/1460419265460018/permalink/1469914231177188/?app=fbl</t>
+    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325658546109448&amp;view=permalink&amp;__cft__[0]=AZZl8Uky_MaylOYDQ8aE22w1YGbyFTAHSI52nonUamoZ2wGLbmalWnu0W0brs0KLbcEWi5Rs2-ZuNOCjZxJbxXz6HZVpuWhRp5bjdEXqX8KMYNv1REDCDA6eFId04yzyKc4&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>1:24.10</t>
+  </si>
+  <si>
+    <t>1:32.28</t>
+  </si>
+  <si>
+    <t>1:38.80</t>
+  </si>
+  <si>
+    <t>1:30.49</t>
+  </si>
+  <si>
+    <t>1:32.74</t>
+  </si>
+  <si>
+    <t>1:31.83</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325664632775506&amp;view=permalink&amp;__cft__[0]=AZatIdItHdwV7hEGVvm2kKbUCKTC89fycILZ-iL9M5SXHBF9MBrmcI0fCe4E8I6g2vNxqAYfJZ4BpRO5Cdv3lP6xYHyRkfe7TmpUzVc2xYRHr-jxVzufO5NWvNpI3YBlCK0&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>5:46.69</t>
+  </si>
+  <si>
+    <t>5:05.84</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325669506108352&amp;view=permalink&amp;__cft__[0]=AZZL-n2TpJpEjoquDAAP-9-EYFeF79k_mnGdxfY0bC6f3SPUY3oJHhLWruNw3u3tNPCz9wGQ7ArAcv_AxfaSQEhiZLHBowiSUIEfbsl7wUwPS10cPR7U4SFDUE_Ya3ZNWms&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>2:38.58</t>
+  </si>
+  <si>
+    <t>2:32.04</t>
+  </si>
+  <si>
+    <t>2:34.46</t>
+  </si>
+  <si>
+    <t>2:35.04</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1599779991315441/?post_id=1609757930317647&amp;view=permalink&amp;__cft__[0]=AZYBamKnijjfZXJrNMoXd21hQSoT-nm9R3iTpEYnMjrJsdCq6aBXttyidQ0wrAzjmiSfZUXjB6QqCSjQOy67W-3VShM7CGaUR06F4Xrwp3UZM2ZYcoxYqIqZk0oqjh9StOc&amp;__tn__=%2CO%2CP-R</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/frederick.g.johnson/videos/857239384079277/?idorvanity=1460419265460018</t>
+  </si>
+  <si>
+    <t>4:22.15</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/events/1460419265460018/?post_id=1469914231177188&amp;view=permalink&amp;__cft__[0]=AZaIby_HxsJuAXXfz4EFs8oWpIGodqJOpIOE-y-SCnijW_HESB3vJ5Toxp-g-e_seBa1ohx0rW52M3j4Z9RUHLMc1e3lsZXQ_EjKWEPSSXvvoRMfBWhnvk7TRdaus4vZRdI&amp;__tn__=%2CO%2CP-R</t>
   </si>
   <si>
     <t>1:34.78</t>
@@ -910,58 +964,7 @@
     <t>1:56.84</t>
   </si>
   <si>
-    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325658546109448&amp;view=permalink&amp;__cft__[0]=AZZl8Uky_MaylOYDQ8aE22w1YGbyFTAHSI52nonUamoZ2wGLbmalWnu0W0brs0KLbcEWi5Rs2-ZuNOCjZxJbxXz6HZVpuWhRp5bjdEXqX8KMYNv1REDCDA6eFId04yzyKc4&amp;__tn__=%2CO%2CP-R</t>
-  </si>
-  <si>
-    <t>1:24.10</t>
-  </si>
-  <si>
-    <t>1:32.28</t>
-  </si>
-  <si>
-    <t>1:38.80</t>
-  </si>
-  <si>
-    <t>1:30.49</t>
-  </si>
-  <si>
-    <t>1:32.74</t>
-  </si>
-  <si>
-    <t>1:31.83</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325664632775506&amp;view=permalink&amp;__cft__[0]=AZatIdItHdwV7hEGVvm2kKbUCKTC89fycILZ-iL9M5SXHBF9MBrmcI0fCe4E8I6g2vNxqAYfJZ4BpRO5Cdv3lP6xYHyRkfe7TmpUzVc2xYRHr-jxVzufO5NWvNpI3YBlCK0&amp;__tn__=%2CO%2CP-R</t>
-  </si>
-  <si>
-    <t>5:46.69</t>
-  </si>
-  <si>
-    <t>5:05.84</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/events/1316158743726095/?post_id=1325669506108352&amp;view=permalink&amp;__cft__[0]=AZZL-n2TpJpEjoquDAAP-9-EYFeF79k_mnGdxfY0bC6f3SPUY3oJHhLWruNw3u3tNPCz9wGQ7ArAcv_AxfaSQEhiZLHBowiSUIEfbsl7wUwPS10cPR7U4SFDUE_Ya3ZNWms&amp;__tn__=%2CO%2CP-R</t>
-  </si>
-  <si>
-    <t>2:38.58</t>
-  </si>
-  <si>
-    <t>2:32.04</t>
-  </si>
-  <si>
-    <t>2:34.46</t>
-  </si>
-  <si>
-    <t>2:35.04</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/events/1599779991315441/?post_id=1609757930317647&amp;view=permalink&amp;__cft__[0]=AZYBamKnijjfZXJrNMoXd21hQSoT-nm9R3iTpEYnMjrJsdCq6aBXttyidQ0wrAzjmiSfZUXjB6QqCSjQOy67W-3VShM7CGaUR06F4Xrwp3UZM2ZYcoxYqIqZk0oqjh9StOc&amp;__tn__=%2CO%2CP-R</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/frederick.g.johnson/videos/857239384079277/?idorvanity=1460419265460018</t>
-  </si>
-  <si>
-    <t>4:22.15</t>
+    <t>https://www.facebook.com/events/1519602439581845/?post_id=1529483965260359&amp;view=permalink&amp;__cft__[0]=AZanqj2aPCnb9bgAb_4Nma9XCqbGJfyHCfcADTV-s07Wv9dx-Xum9ouyxLTa-qhp6LUWFRp3OWYP1Kw8XiKopedJxQ6c5O3I4gI5juLtBicW6FwlT6MwwazTqNtJw8TsCUE&amp;__tn__=%2CO%2CP-R</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1121,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:DH53" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:DH54" displayName="Form_Responses" name="Form_Responses" id="1">
   <tableColumns count="112">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Name" id="2"/>
@@ -3675,48 +3678,48 @@
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="6">
-        <v>46152.51658283565</v>
+        <v>46152.649908611114</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>220</v>
+        <v>138</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="O48" s="7" t="s">
+      <c r="V48" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="P48" s="7" t="s">
+      <c r="W48" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="Q48" s="7" t="s">
+      <c r="X48" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="R48" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S48" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="T48" s="7" t="s">
+      <c r="Y48" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z48" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA48" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="U48" s="7" t="s">
-        <v>119</v>
+      <c r="AB48" s="7" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="6">
-        <v>46152.649908611114</v>
+        <v>46152.65804130787</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>137</v>
@@ -3728,36 +3731,30 @@
         <v>138</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>259</v>
+        <v>166</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="V49" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="W49" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="X49" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="Y49" s="7" t="s">
+      <c r="AJ49" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="Z49" s="7" t="s">
+      <c r="AK49" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="AA49" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="AB49" s="7" t="s">
-        <v>305</v>
+      <c r="AL49" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM49" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="AN49" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="6">
-        <v>46152.65804130787</v>
+        <v>46152.76013790509</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>137</v>
@@ -3769,30 +3766,36 @@
         <v>138</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F50" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="AC50" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="AJ50" s="7" t="s">
+      <c r="AD50" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="AK50" s="7" t="s">
+      <c r="AE50" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="AL50" s="7" t="s">
+      <c r="AF50" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="AM50" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="AN50" s="7" t="s">
-        <v>119</v>
+      <c r="AG50" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH50" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="AI50" s="7" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="6">
-        <v>46152.76013790509</v>
+        <v>46152.765187881945</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>137</v>
@@ -3804,113 +3807,154 @@
         <v>138</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="AC51" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="AD51" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="AE51" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="AF51" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="AG51" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="AH51" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="AI51" s="7" t="s">
-        <v>313</v>
+      <c r="BO51" s="7">
+        <v>11.29</v>
+      </c>
+      <c r="BP51" s="7">
+        <v>16.08</v>
+      </c>
+      <c r="BQ51" s="7">
+        <v>11.36</v>
+      </c>
+      <c r="BR51" s="7">
+        <v>8.09</v>
+      </c>
+      <c r="BS51" s="7">
+        <v>8.24</v>
+      </c>
+      <c r="BT51" s="7">
+        <v>8.09</v>
+      </c>
+      <c r="BU51" s="7">
+        <v>10.29</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="6">
-        <v>46152.765187881945</v>
+        <v>46153.46247165509</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="BO52" s="7">
-        <v>11.29</v>
-      </c>
-      <c r="BP52" s="7">
-        <v>16.08</v>
-      </c>
-      <c r="BQ52" s="7">
-        <v>11.36</v>
-      </c>
-      <c r="BR52" s="7">
-        <v>8.09</v>
-      </c>
-      <c r="BS52" s="7">
-        <v>8.24</v>
-      </c>
-      <c r="BT52" s="7">
-        <v>8.09</v>
-      </c>
-      <c r="BU52" s="7">
-        <v>10.29</v>
+        <v>311</v>
+      </c>
+      <c r="CO52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CP52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CQ52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CR52" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="CS52" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="CT52" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="CU52" s="7" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="6">
-        <v>46153.46247165509</v>
+        <v>46154.645852870366</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>181</v>
+        <v>219</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>208</v>
       </c>
       <c r="F53" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="CO53" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="CP53" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="CO53" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="CP53" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="CQ53" s="7" t="s">
-        <v>119</v>
+        <v>316</v>
       </c>
       <c r="CR53" s="7" t="s">
         <v>119</v>
       </c>
       <c r="CS53" s="7" t="s">
-        <v>316</v>
+        <v>119</v>
       </c>
       <c r="CT53" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="CU53" s="7" t="s">
         <v>119</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="6">
+        <v>46154.64663112268</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="O54" s="7">
+        <v>19.41</v>
+      </c>
+      <c r="P54" s="7">
+        <v>17.49</v>
+      </c>
+      <c r="Q54" s="7">
+        <v>18.63</v>
+      </c>
+      <c r="R54" s="7">
+        <v>15.76</v>
+      </c>
+      <c r="S54" s="7">
+        <v>31.37</v>
+      </c>
+      <c r="T54" s="7">
+        <v>15.76</v>
+      </c>
+      <c r="U54" s="7">
+        <v>18.51</v>
       </c>
     </row>
   </sheetData>
@@ -3967,10 +4011,11 @@
     <hyperlink r:id="rId50" ref="F51"/>
     <hyperlink r:id="rId51" ref="F52"/>
     <hyperlink r:id="rId52" ref="F53"/>
+    <hyperlink r:id="rId53" ref="F54"/>
   </hyperlinks>
-  <drawing r:id="rId53"/>
+  <drawing r:id="rId54"/>
   <tableParts count="1">
-    <tablePart r:id="rId55"/>
+    <tablePart r:id="rId56"/>
   </tableParts>
 </worksheet>
 </file>